--- a/V11.1_ALT/reports/V11.1_ALT_fleet_report.xlsx
+++ b/V11.1_ALT/reports/V11.1_ALT_fleet_report.xlsx
@@ -3127,7 +3127,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>x1 = log lifetime GED+compound exceedances (exposure-confounded)</t>
+          <t>x1 = log lifetime crank-recovery exceedance days (exposure-confounded)</t>
         </is>
       </c>
       <c r="C3" t="n">
